--- a/content/xls/NSO_p_regions_01.01.2026.xlsx
+++ b/content/xls/NSO_p_regions_01.01.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4AFE26-C5E5-4474-8EC1-C3DAC804A171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAC227C-EC54-4DE3-946C-CEBCA1C6D911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -36,12 +36,6 @@
     <t>Болотнинский муниципальный район</t>
   </si>
   <si>
-    <t>Венгеровский муниципальный район</t>
-  </si>
-  <si>
-    <t>Доволенский муниципальный район</t>
-  </si>
-  <si>
     <t>Здвинский муниципальный район</t>
   </si>
   <si>
@@ -87,25 +81,13 @@
     <t>Ордынский муниципальный район</t>
   </si>
   <si>
-    <t>Северный муниципальный район</t>
-  </si>
-  <si>
-    <t>Сузунский муниципальный район</t>
-  </si>
-  <si>
     <t>Татарский муниципальный округ</t>
   </si>
   <si>
     <t>Тогучинский муниципальный район</t>
   </si>
   <si>
-    <t>Убинский муниципальный район</t>
-  </si>
-  <si>
     <t>Усть-Таркский муниципальный район</t>
-  </si>
-  <si>
-    <t>Чановский муниципальный район</t>
   </si>
   <si>
     <t>Черепановский муниципальный район</t>
@@ -193,6 +175,24 @@
   </si>
   <si>
     <t>Количество банкоматов, ед.</t>
+  </si>
+  <si>
+    <t>Венгеровский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Доволенский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Северный муниципальный округ</t>
+  </si>
+  <si>
+    <t>Сузунский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Убинский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Чановский муниципальный округ</t>
   </si>
 </sst>
 </file>
@@ -763,58 +763,58 @@
   <sheetData>
     <row r="1" spans="1:18" s="10" customFormat="1" ht="126.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="N1" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -987,7 +987,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B5" s="14">
         <v>14630</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B6" s="14">
         <v>12574</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="14">
         <v>11776</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="14">
         <v>57989</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="14">
         <v>13325</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="14">
         <v>5291</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="14">
         <v>24203</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="14">
         <v>44354</v>
@@ -1388,7 +1388,7 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="D12" s="3">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E12" s="15">
         <v>0.80800000000000005</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" s="14">
         <v>11524</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14" s="14">
         <v>27615</v>
@@ -1500,7 +1500,7 @@
         <v>0.13300000000000003</v>
       </c>
       <c r="D14" s="3">
-        <v>2.7000000000000024</v>
+        <v>-2.7</v>
       </c>
       <c r="E14" s="15">
         <v>0.84</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="14">
         <v>11205</v>
@@ -1556,7 +1556,7 @@
         <v>0.114</v>
       </c>
       <c r="D15" s="3">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E15" s="15">
         <v>0.84599999999999997</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="14">
         <v>10013</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="14">
         <v>8395</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="14">
         <v>23573</v>
@@ -1724,7 +1724,7 @@
         <v>0.13000000000000003</v>
       </c>
       <c r="D18" s="3">
-        <v>2.0000000000000018</v>
+        <v>-2</v>
       </c>
       <c r="E18" s="15">
         <v>0.85</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B19" s="14">
         <v>40472</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" s="14">
         <v>160478</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="14">
         <v>33533</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B22" s="14">
         <v>7258</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B23" s="14">
         <v>31325</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1">
         <v>12496</v>
@@ -2060,7 +2060,7 @@
         <v>0.24300000000000002</v>
       </c>
       <c r="D24" s="3">
-        <v>3.5000000000000031</v>
+        <v>-3.5</v>
       </c>
       <c r="E24" s="2">
         <v>0.72199999999999998</v>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B25" s="1">
         <v>32597</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B26" s="1">
         <v>10716</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B27" s="1">
         <v>10216</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B28" s="1">
         <v>20330</v>
@@ -2331,7 +2331,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1">
         <v>29097</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B30" s="1">
         <v>13816</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1">
         <v>7668</v>

--- a/content/xls/NSO_p_regions_01.01.2026.xlsx
+++ b/content/xls/NSO_p_regions_01.01.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAC227C-EC54-4DE3-946C-CEBCA1C6D911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BFE7CD-B2FB-4648-836D-EF23E934A2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -162,9 +162,6 @@
     <t>Количество точек финансового доступа, ед.</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников, ед.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Количество торговых точек с сервисом "Выдача наличных на кассе", ед. </t>
   </si>
   <si>
@@ -193,6 +190,9 @@
   </si>
   <si>
     <t>Чановский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников, ед.</t>
   </si>
 </sst>
 </file>
@@ -787,31 +787,31 @@
         <v>26</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>27</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L1" s="16" t="s">
         <v>32</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N1" s="16" t="s">
         <v>31</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P1" s="16" t="s">
         <v>29</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R1" s="9" t="s">
         <v>30</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="14">
         <v>14630</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="14">
         <v>12574</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="14">
         <v>7258</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="14">
         <v>31325</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1">
         <v>10716</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" s="1">
         <v>20330</v>

--- a/content/xls/NSO_p_regions_01.01.2026.xlsx
+++ b/content/xls/NSO_p_regions_01.01.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BFE7CD-B2FB-4648-836D-EF23E934A2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921F4B4A-FA56-4A0B-9918-80F5451D726D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>

--- a/content/xls/NSO_p_regions_01.01.2026.xlsx
+++ b/content/xls/NSO_p_regions_01.01.2026.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Юлия\Desktop\ФД_2026\10.08.26\от Егора_итоговые файлы_25.08.26\Ответ_измен. ур.дбо_зеленым\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921F4B4A-FA56-4A0B-9918-80F5451D726D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F590CBA-44DA-4EDD-BA30-91218C99F073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$S$31</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -290,7 +293,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,15 +331,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -346,7 +340,7 @@
     <cellStyle name="Процентный" xfId="1" builtinId="5"/>
     <cellStyle name="Финансовый" xfId="2" builtinId="3"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="32">
     <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
@@ -355,6 +349,86 @@
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -738,99 +812,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8ED133E-911A-4285-ABEA-63C58E8165A8}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="14.8" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="13.5546875" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1" collapsed="1"/>
     <col min="8" max="8" width="14" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="15" customWidth="1" collapsed="1"/>
     <col min="12" max="12" width="17" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="13.33203125" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="15.33203125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="15.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="15" max="15" width="15" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="15.6640625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="17" max="17" width="16.88671875" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="14.44140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="9.109375" collapsed="1"/>
+    <col min="16" max="16" width="15.7109375" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="17" max="17" width="16.85546875" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="14.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="9.140625" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="10" customFormat="1" ht="126.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:18" s="10" customFormat="1" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="13" t="s">
         <v>40</v>
       </c>
       <c r="R1" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="14">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
         <v>13848</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="2">
         <v>0.22399999999999998</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="2">
         <v>0.77600000000000002</v>
       </c>
       <c r="F2" s="11">
@@ -873,20 +947,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="14">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
         <v>11175</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="2">
         <v>0.22099999999999997</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="2">
         <v>0.77900000000000003</v>
       </c>
       <c r="F3" s="11">
@@ -929,20 +1003,20 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="1">
         <v>9042</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="2">
         <v>0.18999999999999995</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="2">
         <v>0.81</v>
       </c>
       <c r="F4" s="11">
@@ -985,20 +1059,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="1">
         <v>14630</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="2">
         <v>0.16700000000000004</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="2">
         <v>0.83299999999999996</v>
       </c>
       <c r="F5" s="11">
@@ -1041,20 +1115,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="1">
         <v>12574</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="2">
         <v>0.10099999999999998</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="2">
         <v>0.89900000000000002</v>
       </c>
       <c r="F6" s="11">
@@ -1097,20 +1171,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="1">
         <v>11776</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="2">
         <v>0.16700000000000004</v>
       </c>
       <c r="D7" s="3">
         <v>0</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="2">
         <v>0.83299999999999996</v>
       </c>
       <c r="F7" s="11">
@@ -1153,20 +1227,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="1">
         <v>57989</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="2">
         <v>0.21299999999999997</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="2">
         <v>0.78700000000000003</v>
       </c>
       <c r="F8" s="11">
@@ -1209,20 +1283,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="1">
         <v>13325</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="2">
         <v>0.18300000000000005</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="2">
         <v>0.81699999999999995</v>
       </c>
       <c r="F9" s="11">
@@ -1265,20 +1339,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="1">
         <v>5291</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="2">
         <v>0.18600000000000005</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="2">
         <v>0.81399999999999995</v>
       </c>
       <c r="F10" s="11">
@@ -1321,20 +1395,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="1">
         <v>24203</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="2">
         <v>0.15400000000000003</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="2">
         <v>0.84599999999999997</v>
       </c>
       <c r="F11" s="11">
@@ -1377,20 +1451,20 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="1">
         <v>44354</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="2">
         <v>0.16700000000000001</v>
       </c>
       <c r="D12" s="3">
         <v>-2.5</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="2">
         <v>0.80800000000000005</v>
       </c>
       <c r="F12" s="11">
@@ -1433,20 +1507,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="1">
         <v>11524</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="2">
         <v>0.11099999999999999</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="2">
         <v>0.88900000000000001</v>
       </c>
       <c r="F13" s="11">
@@ -1489,20 +1563,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="1">
         <v>27615</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="2">
         <v>0.13300000000000003</v>
       </c>
       <c r="D14" s="3">
         <v>-2.7</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="2">
         <v>0.84</v>
       </c>
       <c r="F14" s="11">
@@ -1545,20 +1619,20 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="1">
         <v>11205</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="2">
         <v>0.114</v>
       </c>
       <c r="D15" s="3">
         <v>-4</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="2">
         <v>0.84599999999999997</v>
       </c>
       <c r="F15" s="11">
@@ -1601,20 +1675,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="1">
         <v>10013</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="2">
         <v>0.17300000000000004</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="2">
         <v>0.82699999999999996</v>
       </c>
       <c r="F16" s="11">
@@ -1657,20 +1731,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="1">
         <v>8395</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="2">
         <v>0.252</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="2">
         <v>0.748</v>
       </c>
       <c r="F17" s="11">
@@ -1713,20 +1787,20 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="1">
         <v>23573</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="2">
         <v>0.13000000000000003</v>
       </c>
       <c r="D18" s="3">
         <v>-2</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="2">
         <v>0.85</v>
       </c>
       <c r="F18" s="11">
@@ -1769,20 +1843,20 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="1">
         <v>40472</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="2">
         <v>0.18000000000000005</v>
       </c>
       <c r="D19" s="3">
         <v>0</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="2">
         <v>0.82</v>
       </c>
       <c r="F19" s="11">
@@ -1825,20 +1899,20 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="1">
         <v>160478</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="2">
         <v>0.15500000000000003</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="2">
         <v>0.84499999999999997</v>
       </c>
       <c r="F20" s="11">
@@ -1881,20 +1955,20 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="1">
         <v>33533</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="2">
         <v>0.125</v>
       </c>
       <c r="D21" s="3">
         <v>0</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="2">
         <v>0.875</v>
       </c>
       <c r="F21" s="11">
@@ -1937,20 +2011,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="1">
         <v>7258</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="2">
         <v>0.14600000000000002</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="2">
         <v>0.85399999999999998</v>
       </c>
       <c r="F22" s="11">
@@ -1993,20 +2067,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="1">
         <v>31325</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="2">
         <v>0.251</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="2">
         <v>0.749</v>
       </c>
       <c r="F23" s="11">
@@ -2049,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>18</v>
       </c>
@@ -2105,7 +2179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>19</v>
       </c>
@@ -2161,7 +2235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>45</v>
       </c>
@@ -2217,7 +2291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>20</v>
       </c>
@@ -2273,7 +2347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>46</v>
       </c>
@@ -2329,7 +2403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>21</v>
       </c>
@@ -2385,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>22</v>
       </c>
@@ -2441,7 +2515,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>23</v>
       </c>
@@ -2497,76 +2571,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D31">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F31">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H31">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J31">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="10" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L31">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N31">
-    <cfRule type="cellIs" dxfId="5" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="15" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="16" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P31">
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="13" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="14" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R31">
-    <cfRule type="cellIs" dxfId="1" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
